--- a/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud</t>
+          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,45</t>
+          <t>1,99; 9,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,89</t>
+          <t>1,22; 3,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,49</t>
+          <t>1,67; 3,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,34</t>
+          <t>1,45; 4,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,42</t>
+          <t>2,09; 8,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 13,63</t>
+          <t>5,58; 13,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,3</t>
+          <t>2,08; 6,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,68</t>
+          <t>2,08; 5,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,75</t>
+          <t>1,4; 10,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,55</t>
+          <t>3,99; 9,89</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,84</t>
+          <t>2,14; 3,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,55</t>
+          <t>1,89; 3,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,83</t>
+          <t>3,25; 4,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,77</t>
+          <t>1,71; 2,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,54</t>
+          <t>1,66; 2,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,46</t>
+          <t>1,54; 2,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,12</t>
+          <t>3,39; 5,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,03</t>
+          <t>1,9; 3,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,88</t>
+          <t>1,98; 2,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,82</t>
+          <t>1,79; 2,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,7</t>
+          <t>3,47; 4,7</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,32</t>
+          <t>1,25; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,96</t>
+          <t>1,57; 2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,38</t>
+          <t>2,1; 4,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,79</t>
+          <t>2,86; 7,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,83</t>
+          <t>2,76; 7,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,95</t>
+          <t>1,0; 5,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,73</t>
+          <t>1,5; 2,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 11,28</t>
+          <t>2,57; 13,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,35</t>
+          <t>2,24; 5,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,77</t>
+          <t>1,58; 3,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,64</t>
+          <t>2,01; 3,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,45</t>
+          <t>3,17; 8,4</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,2</t>
+          <t>2,09; 3,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,24</t>
+          <t>2,08; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,78</t>
+          <t>2,27; 3,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,7</t>
+          <t>3,18; 4,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,68</t>
+          <t>2,15; 3,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,3</t>
+          <t>1,92; 3,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,31</t>
+          <t>1,61; 2,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,65</t>
+          <t>3,99; 6,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,44</t>
+          <t>2,26; 3,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,0</t>
+          <t>2,12; 3,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,9</t>
+          <t>2,01; 2,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,61</t>
+          <t>3,89; 5,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,72</t>
+          <t>1,85; 9,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,66</t>
+          <t>1,22; 3,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,54</t>
+          <t>1,71; 3,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,35</t>
+          <t>1,46; 4,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,57</t>
+          <t>2,13; 8,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 13,55</t>
+          <t>5,71; 13,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,41</t>
+          <t>2,09; 6,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,64</t>
+          <t>1,93; 5,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,06</t>
+          <t>1,36; 10,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,89</t>
+          <t>4,01; 9,66</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,97</t>
+          <t>1,89; 4,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,99</t>
+          <t>2,11; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,67</t>
+          <t>1,88; 3,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,83</t>
+          <t>3,19; 4,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,81</t>
+          <t>1,71; 2,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,53</t>
+          <t>1,67; 2,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,48</t>
+          <t>1,56; 2,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,25</t>
+          <t>3,34; 5,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,05</t>
+          <t>1,92; 2,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,87</t>
+          <t>1,95; 2,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,82</t>
+          <t>1,82; 2,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,7</t>
+          <t>3,46; 4,69</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,34</t>
+          <t>1,25; 2,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,96</t>
+          <t>1,57; 3,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,39</t>
+          <t>2,12; 4,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,38</t>
+          <t>2,95; 7,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,53</t>
+          <t>2,56; 7,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,94</t>
+          <t>1,0; 5,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,72</t>
+          <t>1,44; 2,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 13,24</t>
+          <t>2,52; 11,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,52</t>
+          <t>2,29; 5,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,63</t>
+          <t>1,6; 3,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,59</t>
+          <t>2,07; 3,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,4</t>
+          <t>3,15; 8,52</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,93</t>
+          <t>2,03; 3,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,32</t>
+          <t>2,03; 3,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,83</t>
+          <t>2,26; 3,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,63</t>
+          <t>3,25; 4,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,5</t>
+          <t>2,14; 3,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,24</t>
+          <t>1,94; 3,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,35</t>
+          <t>1,62; 2,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,87</t>
+          <t>3,97; 6,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,27; 3,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,03</t>
+          <t>2,12; 3,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,9</t>
+          <t>2,04; 2,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,5</t>
+          <t>3,88; 5,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo medio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,59</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,88</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,46</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>6,26</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,55</t>
+          <t>1,37; 4,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,64</t>
+          <t>2,05; 8,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>1,0; 3,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5,84; 14,01</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,98; 9,45</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 3,89</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>1,46; 14,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 3,56</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 4,47</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 8,26</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 13,33</t>
+          <t>1,58; 3,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,05</t>
+          <t>2,13; 6,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,69</t>
+          <t>2,02; 5,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 10,04</t>
+          <t>1,38; 9,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 9,66</t>
+          <t>4,06; 9,84</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,99</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,23</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,62</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,89</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,14</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,08</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,08</t>
+          <t>1,71; 2,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,1</t>
+          <t>1,64; 2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,67</t>
+          <t>1,53; 2,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,76</t>
+          <t>3,4; 5,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,8</t>
+          <t>1,89; 3,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,52</t>
+          <t>2,07; 3,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,5</t>
+          <t>1,88; 3,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,12</t>
+          <t>3,14; 4,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,98</t>
+          <t>1,92; 3,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,93</t>
+          <t>1,97; 2,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,85</t>
+          <t>1,83; 2,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,69</t>
+          <t>3,51; 4,74</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,47</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,98</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,68</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,04</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,3</t>
+          <t>2,59; 6,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,05</t>
+          <t>1,0; 5,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,38</t>
+          <t>1,47; 2,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,43</t>
+          <t>2,37; 11,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,21</t>
+          <t>1,25; 2,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,95</t>
+          <t>1,52; 2,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,79</t>
+          <t>2,15; 4,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 11,94</t>
+          <t>2,99; 6,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,58</t>
+          <t>2,22; 5,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,6</t>
+          <t>1,59; 3,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,65</t>
+          <t>2,05; 3,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,52</t>
+          <t>3,15; 8,26</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,72</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,58</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,84</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,54</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,92</t>
+          <t>2,22; 3,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,23</t>
+          <t>1,91; 3,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,87</t>
+          <t>1,58; 2,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,72</t>
+          <t>4,0; 6,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,6</t>
+          <t>2,08; 4,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,29</t>
+          <t>2,04; 3,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,28</t>
+          <t>2,23; 3,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,69</t>
+          <t>3,17; 4,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,39</t>
+          <t>2,27; 3,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,0</t>
+          <t>2,13; 3,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,98</t>
+          <t>2,03; 2,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,51</t>
+          <t>3,86; 5,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,26</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.485229641825372</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4.457748023661997</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.59152186351039</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>8.879827561889355</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>4.488544456676662</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.019617924548121</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>5.296226115462441</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2.329251277078059</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>3.363682349745764</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3.31921429513091</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>3.377694022319063</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>6.258911210088114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 4,34</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2,05; 8,42</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5,84; 14,01</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,98; 9,45</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 3,89</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 14,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 3,31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 6,3</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2,02; 5,68</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,38; 9,75</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,06; 9,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.36551420139649</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.048332687673598</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5.843009719278482</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.983615170343164</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.222415809253927</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.464965258897185</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.581516606628568</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>2.129428213457979</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2.019957867923701</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.382743771812836</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>4.060909603077757</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.338379420978339</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.418935411800504</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.01175043428345</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.448264834523894</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3.892493049662208</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3.309884022598773</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6.299160942092489</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>5.680085420525324</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>9.749143062069905</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>9.842970033769738</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,23</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 2,77</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,64; 2,54</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 2,46</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3,4; 5,32</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,89; 3,97</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,07; 3,84</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,88; 3,55</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3,14; 4,79</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 3,03</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,97; 2,88</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,83; 2,82</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,51; 4,74</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.123436599274853</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.993867950517199</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.89247453132342</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.231982118191629</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2.619615183572605</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>2.892563133801951</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2.502998226426528</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>3.900014435291967</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>2.367763150804736</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>2.360798269742501</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>2.189360404876761</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>4.084635421734046</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,15</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,04</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,29</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.709381708319615</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.641881696047142</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.528514488059798</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>3.399605271172098</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.890038953339096</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>2.068511129591482</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.875253513465354</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>3.141772493234821</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.915452988297979</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.972111438443997</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.825079001155429</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>3.514438691160086</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,59; 6,83</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 5,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 2,73</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2,37; 11,42</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 2,32</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 2,96</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,15; 4,38</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2,99; 6,84</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 5,35</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 3,77</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2,05; 3,64</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,15; 8,26</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.769618605361572</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.542823517289323</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.460266863217497</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.316775540046931</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3.971287088036271</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3.835414182617265</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>3.548709304802159</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>4.794228575221873</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>3.028102965292467</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2.88191114485441</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.821807550886908</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>4.736580813732703</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.317664202554248</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.466510086443344</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.984239949335447</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.974220298970172</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.682008672658243</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.147872108285704</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3.035481359630297</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4.28797288869303</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>3.370025394670305</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2.272851528432706</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>2.669837477012699</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>4.647343586995698</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 3,68</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,91; 3,3</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 2,31</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,0; 6,87</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,08; 4,2</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,04; 3,24</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 3,78</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3,17; 4,72</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2,27; 3,44</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 3,0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 2,9</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,86; 5,59</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2.586652467383403</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.46575741208794</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>2.374404410419398</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.254940269541888</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.520312710305695</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>2.152465292914993</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2.987451714108099</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>2.215397615936891</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.588543752588532</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>2.052969162821868</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>3.153487050051452</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.831682964388471</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.951874515996488</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.72676893502981</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.41634320354485</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.324439173244973</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.964610040226826</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>4.375194272683717</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>6.840493684744331</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5.351181291648046</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>3.767618774167093</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>3.644628596465764</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>8.258339890392614</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.7157473084031</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.426476008722199</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.888457339479541</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5.119087206083094</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>2.765330607319737</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2.581378663833384</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2.836747089976419</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>3.81203381734404</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2.738368050166753</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>2.496365718461826</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>2.389753085717961</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>4.535792516445901</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2.219361632368277</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.909241447837609</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.580688733570163</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>3.99926108856692</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.083811240031952</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>2.03676227362654</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2.232357368784571</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>3.16509917571241</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>2.265020926931364</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>2.125380395995036</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>2.031956874367103</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>3.862592635105313</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.675658098589313</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.298807477853323</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.308832055243021</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.86776841469084</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>4.195253122394644</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3.236412504667187</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3.783151226843438</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>4.7216976878265</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>3.439103805410435</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2.999988775499292</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2.897774504835769</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>5.594812000573126</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
